--- a/minio-report-tracker/xlxs/qa-base.xlsx
+++ b/minio-report-tracker/xlxs/qa-base.xlsx
@@ -356,31 +356,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>198</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7620000" cy="3810000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -676,7 +651,7 @@
   <dimension ref="A1:AR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
@@ -685,7 +660,7 @@
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
@@ -694,16 +669,16 @@
     <col width="5" customWidth="1" min="16" max="16"/>
     <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
     <col width="5" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
     <col width="5" customWidth="1" min="31" max="31"/>
@@ -712,7 +687,7 @@
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
-    <col width="18" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
     <col width="5" customWidth="1" min="40" max="40"/>
@@ -927,7 +902,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -942,177 +917,177 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>578</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>26-March-2026</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>25-March-2026</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>24-March-2026</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>23-March-2026</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>11-December-2025</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>10-December-2025</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09-December-2025</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>08-December-2025</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1129,7 +1104,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1169,87 +1144,87 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>25-March-2026</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>10-December-2025</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09-December-2025</t>
+          <t>24-March-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1289,7 +1264,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>08-December-2025</t>
+          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1304,7 +1279,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>896</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1314,7 +1289,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1331,7 +1306,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1371,99 +1346,99 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>25-March-2026</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>10-December-2025</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>24-March-2026</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09-December-2025</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
       <c r="AE4" t="inlineStr">
         <is>
           <t>923</t>
@@ -1491,7 +1466,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>08-December-2025</t>
+          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1533,7 +1508,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1573,99 +1548,99 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>25-March-2026</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>10-December-2025</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>24-March-2026</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09-December-2025</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
           <t>907</t>
@@ -1693,7 +1668,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>08-December-2025</t>
+          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1735,7 +1710,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1775,87 +1750,87 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>25-March-2026</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>10-December-2025</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09-December-2025</t>
+          <t>24-March-2026</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1895,7 +1870,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>08-December-2025</t>
+          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1937,7 +1912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1952,17 +1927,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>213</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1977,87 +1952,87 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>25-March-2026</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>10-December-2025</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09-December-2025</t>
+          <t>24-March-2026</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -2072,17 +2047,17 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -2097,7 +2072,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>08-December-2025</t>
+          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2112,17 +2087,17 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -2139,7 +2114,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2154,17 +2129,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>476</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2179,32 +2154,32 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11-December-2025</t>
+          <t>26-March-2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>residentui</t>
+          <t>Adminui</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2219,47 +2194,47 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>prereg</t>
+          <t>resident</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>585</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>475</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09-December-2025</t>
+          <t>24-March-2026</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -2274,17 +2249,17 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>582</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -2299,7 +2274,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>08-December-2025</t>
+          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2319,12 +2294,12 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -2341,7 +2316,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2379,116 +2354,100 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>11-December-2025</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Adminui</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="J9" t="n">
+        <v/>
+      </c>
+      <c r="K9" t="n">
+        <v/>
+      </c>
+      <c r="L9" t="n">
+        <v/>
+      </c>
+      <c r="M9" t="n">
+        <v/>
+      </c>
+      <c r="N9" t="n">
+        <v/>
+      </c>
+      <c r="O9" t="n">
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v/>
+      </c>
+      <c r="Q9" t="n">
+        <v/>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>25-March-2026</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>24-March-2026</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>10-December-2025</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09-December-2025</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2501,7 +2460,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>08-December-2025</t>
+          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2543,7 +2502,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12-December-2025</t>
+          <t>27-March-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2607,7 +2566,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>10-December-2025</t>
+          <t>25-March-2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -2647,7 +2606,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09-December-2025</t>
+          <t>24-March-2026</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2687,7 +2646,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>08-December-2025</t>
+          <t>23-March-2026</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa-base.xlsx
+++ b/minio-report-tracker/xlxs/qa-base.xlsx
@@ -671,12 +671,12 @@
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
     <col width="5" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
     <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -853,129 +853,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>577</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>578</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>26-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>residentui</t>
@@ -988,7 +988,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1015,127 +1015,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>25-March-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1177,122 +1177,122 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -1323,122 +1323,122 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1469,122 +1469,122 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1615,122 +1615,122 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1761,122 +1761,122 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>587</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>473</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>586</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>476</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Adminui</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AB8" t="n">
@@ -1907,107 +1907,123 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v/>
-      </c>
-      <c r="T9" t="n">
-        <v/>
-      </c>
-      <c r="U9" t="n">
-        <v/>
-      </c>
-      <c r="V9" t="n">
-        <v/>
-      </c>
-      <c r="W9" t="n">
-        <v/>
-      </c>
-      <c r="X9" t="n">
-        <v/>
-      </c>
-      <c r="Y9" t="n">
-        <v/>
-      </c>
-      <c r="Z9" t="n">
-        <v/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="AB9" t="n">
         <v/>
@@ -2037,107 +2053,123 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>31-March-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adminui</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v/>
-      </c>
-      <c r="T10" t="n">
-        <v/>
-      </c>
-      <c r="U10" t="n">
-        <v/>
-      </c>
-      <c r="V10" t="n">
-        <v/>
-      </c>
-      <c r="W10" t="n">
-        <v/>
-      </c>
-      <c r="X10" t="n">
-        <v/>
-      </c>
-      <c r="Y10" t="n">
-        <v/>
-      </c>
-      <c r="Z10" t="n">
-        <v/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="AB10" t="n">
         <v/>

--- a/minio-report-tracker/xlxs/qa-base.xlsx
+++ b/minio-report-tracker/xlxs/qa-base.xlsx
@@ -853,152 +853,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>577</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>27-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1015,127 +1015,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>26-March-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1177,87 +1177,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1323,87 +1323,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1469,87 +1469,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1615,87 +1615,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1761,112 +1761,112 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>578</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>587</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>473</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>476</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1907,87 +1907,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2053,87 +2053,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>01-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adminui</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Adminui</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa-base.xlsx
+++ b/minio-report-tracker/xlxs/qa-base.xlsx
@@ -679,13 +679,13 @@
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
     <col width="5" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
     <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="4" customWidth="1" min="34" max="34"/>
+    <col width="4" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -853,1347 +853,1459 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>577</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>27-March-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Adminui</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
-      </c>
-      <c r="AB4" t="n">
-        <v/>
-      </c>
-      <c r="AC4" t="n">
-        <v/>
-      </c>
-      <c r="AD4" t="n">
-        <v/>
-      </c>
-      <c r="AE4" t="n">
-        <v/>
-      </c>
-      <c r="AF4" t="n">
-        <v/>
-      </c>
-      <c r="AG4" t="n">
-        <v/>
-      </c>
-      <c r="AH4" t="n">
-        <v/>
-      </c>
-      <c r="AI4" t="n">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
-      </c>
-      <c r="AB5" t="n">
-        <v/>
-      </c>
-      <c r="AC5" t="n">
-        <v/>
-      </c>
-      <c r="AD5" t="n">
-        <v/>
-      </c>
-      <c r="AE5" t="n">
-        <v/>
-      </c>
-      <c r="AF5" t="n">
-        <v/>
-      </c>
-      <c r="AG5" t="n">
-        <v/>
-      </c>
-      <c r="AH5" t="n">
-        <v/>
-      </c>
-      <c r="AI5" t="n">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>584</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>474</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>578</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>587</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>473</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v/>
-      </c>
-      <c r="AC9" t="n">
-        <v/>
-      </c>
-      <c r="AD9" t="n">
-        <v/>
-      </c>
-      <c r="AE9" t="n">
-        <v/>
-      </c>
-      <c r="AF9" t="n">
-        <v/>
-      </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="n">
-        <v/>
-      </c>
-      <c r="AI9" t="n">
-        <v/>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>02-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adminui</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v/>
-      </c>
-      <c r="AC10" t="n">
-        <v/>
-      </c>
-      <c r="AD10" t="n">
-        <v/>
-      </c>
-      <c r="AE10" t="n">
-        <v/>
-      </c>
-      <c r="AF10" t="n">
-        <v/>
-      </c>
-      <c r="AG10" t="n">
-        <v/>
-      </c>
-      <c r="AH10" t="n">
-        <v/>
-      </c>
-      <c r="AI10" t="n">
-        <v/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qa-base.xlsx
+++ b/minio-report-tracker/xlxs/qa-base.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -686,6 +686,15 @@
     <col width="5" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
+    <col width="2" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="6" customWidth="1" min="39" max="39"/>
+    <col width="5" customWidth="1" min="40" max="40"/>
+    <col width="5" customWidth="1" min="41" max="41"/>
+    <col width="5" customWidth="1" min="42" max="42"/>
+    <col width="4" customWidth="1" min="43" max="43"/>
+    <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -849,164 +858,244 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>577</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1015,160 +1104,200 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>891</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -1177,160 +1306,200 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>754</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -1339,160 +1508,200 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>902</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -1501,160 +1710,200 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1663,160 +1912,200 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1825,160 +2114,200 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>583</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>475</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>584</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>474</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>578</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>587</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>473</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1987,160 +2316,200 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -2149,160 +2518,200 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>03-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adminui</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>31-March-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>30-March-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa-base.xlsx
+++ b/minio-report-tracker/xlxs/qa-base.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR10"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -679,22 +679,13 @@
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
-    <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="5" customWidth="1" min="30" max="30"/>
     <col width="5" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
     <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="4" customWidth="1" min="34" max="34"/>
-    <col width="4" customWidth="1" min="35" max="35"/>
-    <col width="2" customWidth="1" min="36" max="36"/>
-    <col width="15" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
-    <col width="6" customWidth="1" min="39" max="39"/>
-    <col width="5" customWidth="1" min="40" max="40"/>
-    <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="5" customWidth="1" min="42" max="42"/>
-    <col width="4" customWidth="1" min="43" max="43"/>
-    <col width="4" customWidth="1" min="44" max="44"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -858,388 +849,308 @@
           <t>KI</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>KI</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>891</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>01-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>masterdata-ara</t>
+          <t>Adminui</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1254,1176 +1165,856 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>754</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="AB4" t="n">
+        <v/>
+      </c>
+      <c r="AC4" t="n">
+        <v/>
+      </c>
+      <c r="AD4" t="n">
+        <v/>
+      </c>
+      <c r="AE4" t="n">
+        <v/>
+      </c>
+      <c r="AF4" t="n">
+        <v/>
+      </c>
+      <c r="AG4" t="n">
+        <v/>
+      </c>
+      <c r="AH4" t="n">
+        <v/>
+      </c>
+      <c r="AI4" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>902</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="AB5" t="n">
+        <v/>
+      </c>
+      <c r="AC5" t="n">
+        <v/>
+      </c>
+      <c r="AD5" t="n">
+        <v/>
+      </c>
+      <c r="AE5" t="n">
+        <v/>
+      </c>
+      <c r="AF5" t="n">
+        <v/>
+      </c>
+      <c r="AG5" t="n">
+        <v/>
+      </c>
+      <c r="AH5" t="n">
+        <v/>
+      </c>
+      <c r="AI5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB6" t="n">
+        <v/>
+      </c>
+      <c r="AC6" t="n">
+        <v/>
+      </c>
+      <c r="AD6" t="n">
+        <v/>
+      </c>
+      <c r="AE6" t="n">
+        <v/>
+      </c>
+      <c r="AF6" t="n">
+        <v/>
+      </c>
+      <c r="AG6" t="n">
+        <v/>
+      </c>
+      <c r="AH6" t="n">
+        <v/>
+      </c>
+      <c r="AI6" t="n">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="AB7" t="n">
+        <v/>
+      </c>
+      <c r="AC7" t="n">
+        <v/>
+      </c>
+      <c r="AD7" t="n">
+        <v/>
+      </c>
+      <c r="AE7" t="n">
+        <v/>
+      </c>
+      <c r="AF7" t="n">
+        <v/>
+      </c>
+      <c r="AG7" t="n">
+        <v/>
+      </c>
+      <c r="AH7" t="n">
+        <v/>
+      </c>
+      <c r="AI7" t="n">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>584</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>474</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>583</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>475</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="AB8" t="n">
+        <v/>
+      </c>
+      <c r="AC8" t="n">
+        <v/>
+      </c>
+      <c r="AD8" t="n">
+        <v/>
+      </c>
+      <c r="AE8" t="n">
+        <v/>
+      </c>
+      <c r="AF8" t="n">
+        <v/>
+      </c>
+      <c r="AG8" t="n">
+        <v/>
+      </c>
+      <c r="AH8" t="n">
+        <v/>
+      </c>
+      <c r="AI8" t="n">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2434,188 +2025,132 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AB9" t="n">
+        <v/>
+      </c>
+      <c r="AC9" t="n">
+        <v/>
+      </c>
+      <c r="AD9" t="n">
+        <v/>
+      </c>
+      <c r="AE9" t="n">
+        <v/>
+      </c>
+      <c r="AF9" t="n">
+        <v/>
+      </c>
+      <c r="AG9" t="n">
+        <v/>
+      </c>
+      <c r="AH9" t="n">
+        <v/>
+      </c>
+      <c r="AI9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>06-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adminui</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>02-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Adminui</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>0</t>
@@ -2636,85 +2171,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>31-March-2026</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Adminui</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>30-March-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Adminui</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AB10" t="n">
+        <v/>
+      </c>
+      <c r="AC10" t="n">
+        <v/>
+      </c>
+      <c r="AD10" t="n">
+        <v/>
+      </c>
+      <c r="AE10" t="n">
+        <v/>
+      </c>
+      <c r="AF10" t="n">
+        <v/>
+      </c>
+      <c r="AG10" t="n">
+        <v/>
+      </c>
+      <c r="AH10" t="n">
+        <v/>
+      </c>
+      <c r="AI10" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qa-base.xlsx
+++ b/minio-report-tracker/xlxs/qa-base.xlsx
@@ -853,127 +853,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1015,127 +1015,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>01-April-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1177,112 +1177,112 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1323,112 +1323,112 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1469,87 +1469,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1615,87 +1615,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1761,112 +1761,112 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>578</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>03-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>584</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>474</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>475</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1907,87 +1907,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2053,87 +2053,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adminui</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Adminui</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa-base.xlsx
+++ b/minio-report-tracker/xlxs/qa-base.xlsx
@@ -853,127 +853,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1015,127 +1015,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>02-April-2026</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1177,87 +1177,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1323,87 +1323,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1469,87 +1469,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1615,87 +1615,87 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1761,112 +1761,112 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>575</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>483</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>578</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>480</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>474</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1907,87 +1907,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -2053,87 +2053,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>08-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adminui</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>06-April-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Adminui</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qa-base.xlsx
+++ b/minio-report-tracker/xlxs/qa-base.xlsx
@@ -679,13 +679,13 @@
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="5" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
     <col width="5" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
     <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="4" customWidth="1" min="34" max="34"/>
+    <col width="4" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -853,1347 +853,1459 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>residentui</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>03-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Adminui</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
-      </c>
-      <c r="AB4" t="n">
-        <v/>
-      </c>
-      <c r="AC4" t="n">
-        <v/>
-      </c>
-      <c r="AD4" t="n">
-        <v/>
-      </c>
-      <c r="AE4" t="n">
-        <v/>
-      </c>
-      <c r="AF4" t="n">
-        <v/>
-      </c>
-      <c r="AG4" t="n">
-        <v/>
-      </c>
-      <c r="AH4" t="n">
-        <v/>
-      </c>
-      <c r="AI4" t="n">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
-      </c>
-      <c r="AB5" t="n">
-        <v/>
-      </c>
-      <c r="AC5" t="n">
-        <v/>
-      </c>
-      <c r="AD5" t="n">
-        <v/>
-      </c>
-      <c r="AE5" t="n">
-        <v/>
-      </c>
-      <c r="AF5" t="n">
-        <v/>
-      </c>
-      <c r="AG5" t="n">
-        <v/>
-      </c>
-      <c r="AH5" t="n">
-        <v/>
-      </c>
-      <c r="AI5" t="n">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="AB6" t="n">
-        <v/>
-      </c>
-      <c r="AC6" t="n">
-        <v/>
-      </c>
-      <c r="AD6" t="n">
-        <v/>
-      </c>
-      <c r="AE6" t="n">
-        <v/>
-      </c>
-      <c r="AF6" t="n">
-        <v/>
-      </c>
-      <c r="AG6" t="n">
-        <v/>
-      </c>
-      <c r="AH6" t="n">
-        <v/>
-      </c>
-      <c r="AI6" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
-      </c>
-      <c r="AB7" t="n">
-        <v/>
-      </c>
-      <c r="AC7" t="n">
-        <v/>
-      </c>
-      <c r="AD7" t="n">
-        <v/>
-      </c>
-      <c r="AE7" t="n">
-        <v/>
-      </c>
-      <c r="AF7" t="n">
-        <v/>
-      </c>
-      <c r="AG7" t="n">
-        <v/>
-      </c>
-      <c r="AH7" t="n">
-        <v/>
-      </c>
-      <c r="AI7" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>583</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>475</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>575</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>483</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>578</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
-      </c>
-      <c r="AB8" t="n">
-        <v/>
-      </c>
-      <c r="AC8" t="n">
-        <v/>
-      </c>
-      <c r="AD8" t="n">
-        <v/>
-      </c>
-      <c r="AE8" t="n">
-        <v/>
-      </c>
-      <c r="AF8" t="n">
-        <v/>
-      </c>
-      <c r="AG8" t="n">
-        <v/>
-      </c>
-      <c r="AH8" t="n">
-        <v/>
-      </c>
-      <c r="AI8" t="n">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v/>
-      </c>
-      <c r="AC9" t="n">
-        <v/>
-      </c>
-      <c r="AD9" t="n">
-        <v/>
-      </c>
-      <c r="AE9" t="n">
-        <v/>
-      </c>
-      <c r="AF9" t="n">
-        <v/>
-      </c>
-      <c r="AG9" t="n">
-        <v/>
-      </c>
-      <c r="AH9" t="n">
-        <v/>
-      </c>
-      <c r="AI9" t="n">
-        <v/>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>09-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adminui</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v/>
-      </c>
-      <c r="AC10" t="n">
-        <v/>
-      </c>
-      <c r="AD10" t="n">
-        <v/>
-      </c>
-      <c r="AE10" t="n">
-        <v/>
-      </c>
-      <c r="AF10" t="n">
-        <v/>
-      </c>
-      <c r="AG10" t="n">
-        <v/>
-      </c>
-      <c r="AH10" t="n">
-        <v/>
-      </c>
-      <c r="AI10" t="n">
-        <v/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qa-base.xlsx
+++ b/minio-report-tracker/xlxs/qa-base.xlsx
@@ -648,17 +648,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -686,6 +686,15 @@
     <col width="5" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
+    <col width="2" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="6" customWidth="1" min="39" max="39"/>
+    <col width="5" customWidth="1" min="40" max="40"/>
+    <col width="5" customWidth="1" min="41" max="41"/>
+    <col width="5" customWidth="1" min="42" max="42"/>
+    <col width="4" customWidth="1" min="43" max="43"/>
+    <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -849,164 +858,244 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1015,160 +1104,200 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -1177,160 +1306,200 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -1339,160 +1508,200 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -1501,160 +1710,200 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1663,160 +1912,200 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1825,160 +2114,200 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>584</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>474</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>583</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>475</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>575</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>483</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>578</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1987,322 +2316,386 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>10-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Adminui</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v/>
+      </c>
+      <c r="B10" t="n">
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v/>
+      </c>
+      <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v/>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>09-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>08-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>07-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>06-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/minio-report-tracker/xlxs/qa-base.xlsx
+++ b/minio-report-tracker/xlxs/qa-base.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -661,13 +661,22 @@
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -751,84 +760,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>478</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>15-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -837,528 +926,848 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
+        <v/>
+      </c>
+      <c r="T3" t="n">
+        <v/>
+      </c>
+      <c r="U3" t="n">
+        <v/>
+      </c>
+      <c r="V3" t="n">
+        <v/>
+      </c>
+      <c r="W3" t="n">
+        <v/>
+      </c>
+      <c r="X3" t="n">
+        <v/>
+      </c>
+      <c r="Y3" t="n">
+        <v/>
+      </c>
+      <c r="Z3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
+        <v/>
+      </c>
+      <c r="T4" t="n">
+        <v/>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" t="n">
+        <v/>
+      </c>
+      <c r="W4" t="n">
+        <v/>
+      </c>
+      <c r="X4" t="n">
+        <v/>
+      </c>
+      <c r="Y4" t="n">
+        <v/>
+      </c>
+      <c r="Z4" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
+        <v/>
+      </c>
+      <c r="T5" t="n">
+        <v/>
+      </c>
+      <c r="U5" t="n">
+        <v/>
+      </c>
+      <c r="V5" t="n">
+        <v/>
+      </c>
+      <c r="W5" t="n">
+        <v/>
+      </c>
+      <c r="X5" t="n">
+        <v/>
+      </c>
+      <c r="Y5" t="n">
+        <v/>
+      </c>
+      <c r="Z5" t="n">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>907</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
+        <v/>
+      </c>
+      <c r="T6" t="n">
+        <v/>
+      </c>
+      <c r="U6" t="n">
+        <v/>
+      </c>
+      <c r="V6" t="n">
+        <v/>
+      </c>
+      <c r="W6" t="n">
+        <v/>
+      </c>
+      <c r="X6" t="n">
+        <v/>
+      </c>
+      <c r="Y6" t="n">
+        <v/>
+      </c>
+      <c r="Z6" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>304</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>159</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
+        <v/>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" t="n">
+        <v/>
+      </c>
+      <c r="V7" t="n">
+        <v/>
+      </c>
+      <c r="W7" t="n">
+        <v/>
+      </c>
+      <c r="X7" t="n">
+        <v/>
+      </c>
+      <c r="Y7" t="n">
+        <v/>
+      </c>
+      <c r="Z7" t="n">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>167</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
+        <v/>
+      </c>
+      <c r="T8" t="n">
+        <v/>
+      </c>
+      <c r="U8" t="n">
+        <v/>
+      </c>
+      <c r="V8" t="n">
+        <v/>
+      </c>
+      <c r="W8" t="n">
+        <v/>
+      </c>
+      <c r="X8" t="n">
+        <v/>
+      </c>
+      <c r="Y8" t="n">
+        <v/>
+      </c>
+      <c r="Z8" t="n">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>residentui</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>residentui</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
-      <c r="Q9" t="n">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v/>
+      </c>
+      <c r="T9" t="n">
+        <v/>
+      </c>
+      <c r="U9" t="n">
+        <v/>
+      </c>
+      <c r="V9" t="n">
+        <v/>
+      </c>
+      <c r="W9" t="n">
+        <v/>
+      </c>
+      <c r="X9" t="n">
+        <v/>
+      </c>
+      <c r="Y9" t="n">
+        <v/>
+      </c>
+      <c r="Z9" t="n">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adminui</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Adminui</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
-      <c r="Q10" t="n">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v/>
+      </c>
+      <c r="T10" t="n">
+        <v/>
+      </c>
+      <c r="U10" t="n">
+        <v/>
+      </c>
+      <c r="V10" t="n">
+        <v/>
+      </c>
+      <c r="W10" t="n">
+        <v/>
+      </c>
+      <c r="X10" t="n">
+        <v/>
+      </c>
+      <c r="Y10" t="n">
+        <v/>
+      </c>
+      <c r="Z10" t="n">
         <v/>
       </c>
     </row>
